--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.3 客户服务信息/1. 客户绑定记录.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.3 客户服务信息/1. 客户绑定记录.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="136">
   <si>
     <t>业务属性</t>
   </si>
@@ -235,10 +235,10 @@
     <t>客户服务信息</t>
   </si>
   <si>
-    <t>客户绑定记录的唯一主键标识。</t>
-  </si>
-  <si>
-    <t>主键，自增标识，非空。</t>
+    <t>客户绑定记录唯一标识，关联客户与表卡/缴费账户的绑定关系。</t>
+  </si>
+  <si>
+    <t>唯一，不可重复，由系统生成。</t>
   </si>
   <si>
     <t/>
@@ -271,7 +271,7 @@
     <t>仅允许数字</t>
   </si>
   <si>
-    <t>符合字段类型及业务字典约束</t>
+    <t>唯一编码，由系统生成。</t>
   </si>
   <si>
     <t>是</t>
@@ -292,10 +292,10 @@
     <t>CARD_ID</t>
   </si>
   <si>
-    <t>绑定业务所对应的水表档案编号。</t>
-  </si>
-  <si>
-    <t>表卡唯一标识，非空。</t>
+    <t>客户所绑定或持有的水表（IC卡）表卡编号，外键关联表卡信息。</t>
+  </si>
+  <si>
+    <t>须匹配表卡信息中存在的表卡编号。</t>
   </si>
   <si>
     <t>VARCHAR2</t>
@@ -307,7 +307,7 @@
     <t>仅允许字符及数字</t>
   </si>
   <si>
-    <t>关联表卡信息表(CM_METERCARDS)</t>
+    <t>须存在于表卡信息表。</t>
   </si>
   <si>
     <t>RCM_BIND_TYPE</t>
@@ -319,15 +319,18 @@
     <t>BIND_TYPE</t>
   </si>
   <si>
-    <t>客户绑定渠道或方式，目前只有微信。</t>
-  </si>
-  <si>
-    <t>引用绑定类型字典，非空。</t>
+    <t>标识客户与表卡/账户绑定方式（如微信）。</t>
+  </si>
+  <si>
+    <t>固定值</t>
   </si>
   <si>
     <t>TYPE_BIND_TYPE</t>
   </si>
   <si>
+    <t>微信。</t>
+  </si>
+  <si>
     <t>RCM_BIND_ACCOUNT</t>
   </si>
   <si>
@@ -337,10 +340,13 @@
     <t>BIND_ACCOUNT</t>
   </si>
   <si>
-    <t>客户绑定服务时使用的外部账号或 OpenID / 手机号。</t>
-  </si>
-  <si>
-    <t>绑定用户标识，非空。</t>
+    <t>绑定账户标识，关联缴费账户。</t>
+  </si>
+  <si>
+    <t>须为有效缴费账户。</t>
+  </si>
+  <si>
+    <t>有效缴费账户标识。</t>
   </si>
   <si>
     <t>中</t>
@@ -358,10 +364,10 @@
     <t>BIND_TIME</t>
   </si>
   <si>
-    <t>客户执行账号绑定操作的时间戳。</t>
-  </si>
-  <si>
-    <t>标准日期时间格式，非空。</t>
+    <t>绑定操作发生的时间。</t>
+  </si>
+  <si>
+    <t>绑定时由系统自动记录。</t>
   </si>
   <si>
     <t>DATE</t>
@@ -373,6 +379,9 @@
     <t>YYYY-MM-DD HH:24:MI:SS</t>
   </si>
   <si>
+    <t>合法日期时间。</t>
+  </si>
+  <si>
     <t>RCM_BIND_STATE</t>
   </si>
   <si>
@@ -382,16 +391,16 @@
     <t>BIND_STATE</t>
   </si>
   <si>
-    <t>账户当前的绑定有效状态。</t>
-  </si>
-  <si>
-    <t>1代表绑定，-1代表解绑。</t>
+    <t>绑定状态代码，包括绑定、解绑。</t>
+  </si>
+  <si>
+    <t>取值以状态字典为准；解绑后更新为解绑。</t>
   </si>
   <si>
     <t>TYPE_BIND_STATE</t>
   </si>
   <si>
-    <t>1绑定,-1解绑</t>
+    <t>1-绑定、-1-解绑</t>
   </si>
   <si>
     <t>否</t>
@@ -406,10 +415,13 @@
     <t>UNBIND_TIME</t>
   </si>
   <si>
-    <t>客户解绑账号操作的时间戳。</t>
-  </si>
-  <si>
-    <t>解绑时填入标准日期时间。</t>
+    <t>解绑操作发生的时间。</t>
+  </si>
+  <si>
+    <t>解绑时由系统自动记录。</t>
+  </si>
+  <si>
+    <t>合法日期时间，可空。</t>
   </si>
 </sst>
 </file>
@@ -455,11 +467,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -836,7 +846,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -856,6 +866,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -960,19 +985,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -981,7 +1006,7 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -990,13 +1015,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1014,28 +1039,28 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1044,10 +1069,10 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1105,7 +1130,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1119,56 +1144,59 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1847,13 +1875,13 @@
       <c r="X4" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="5" t="s">
         <v>85</v>
       </c>
       <c r="AB4" s="4" t="s">
@@ -1939,13 +1967,13 @@
       <c r="X5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AA5" s="5" t="s">
         <v>97</v>
       </c>
       <c r="AB5" s="4" t="s">
@@ -2031,14 +2059,14 @@
       <c r="X6" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AA6" s="4" t="s">
-        <v>85</v>
+      <c r="AA6" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="AB6" s="4" t="s">
         <v>86</v>
@@ -2052,13 +2080,13 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="1:30">
       <c r="A7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>69</v>
@@ -2073,10 +2101,10 @@
         <v>72</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>75</v>
@@ -2123,34 +2151,34 @@
       <c r="X7" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AA7" s="4" t="s">
-        <v>85</v>
+      <c r="AA7" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="AB7" s="4" t="s">
         <v>86</v>
       </c>
       <c r="AC7" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AD7" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1" spans="1:30">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>69</v>
@@ -2165,10 +2193,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>75</v>
@@ -2189,10 +2217,10 @@
         <v>77</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="R8" s="15">
         <v>7</v>
@@ -2215,14 +2243,14 @@
       <c r="X8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z8" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA8" s="4" t="s">
-        <v>85</v>
+        <v>120</v>
+      </c>
+      <c r="AA8" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="AB8" s="4" t="s">
         <v>86</v>
@@ -2236,13 +2264,13 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:30">
       <c r="A9" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>69</v>
@@ -2257,16 +2285,16 @@
         <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>75</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>76</v>
@@ -2307,17 +2335,17 @@
       <c r="X9" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z9" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="AA9" s="4" t="s">
-        <v>125</v>
+      <c r="AA9" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="AB9" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AC9" s="4" t="s">
         <v>87</v>
@@ -2328,13 +2356,13 @@
     </row>
     <row r="10" ht="26" customHeight="1" spans="1:30">
       <c r="A10" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>69</v>
@@ -2349,10 +2377,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>75</v>
@@ -2373,10 +2401,10 @@
         <v>77</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="R10" s="15">
         <v>7</v>
@@ -2399,17 +2427,17 @@
       <c r="X10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="22" t="s">
         <v>83</v>
       </c>
       <c r="Z10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA10" s="4" t="s">
-        <v>85</v>
+        <v>120</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="AB10" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AC10" s="4" t="s">
         <v>87</v>
